--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1050,6 +1050,234 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128637044</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56566</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, Källarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>451423</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6392265</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Barnarp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mattis Arveström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mattis Arveström, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128637073</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56571</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, Källarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>451423</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6392265</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Barnarp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mattis Arveström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mattis Arveström, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>128637044</v>
       </c>
       <c r="B5" t="n">
-        <v>56566</v>
+        <v>56570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>128637073</v>
       </c>
       <c r="B6" t="n">
-        <v>56571</v>
+        <v>56575</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74601884</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451316.7455551541</v>
+        <v>451317</v>
       </c>
       <c r="R2" t="n">
-        <v>6392258.842000017</v>
+        <v>6392259</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1976-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1976-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74604425</v>
       </c>
       <c r="B3" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451316.7455551541</v>
+        <v>451317</v>
       </c>
       <c r="R3" t="n">
-        <v>6392258.842000017</v>
+        <v>6392259</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1976-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1976-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>75143870</v>
       </c>
       <c r="B4" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451316.7455551541</v>
+        <v>451317</v>
       </c>
       <c r="R4" t="n">
-        <v>6392258.842000017</v>
+        <v>6392259</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1976-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1976-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>75143870</v>
       </c>
       <c r="B4" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601884</v>
       </c>
       <c r="B2" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74604425</v>
       </c>
       <c r="B3" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>75143870</v>
       </c>
       <c r="B4" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601884</v>
       </c>
       <c r="B2" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74604425</v>
       </c>
       <c r="B3" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>75143870</v>
       </c>
       <c r="B4" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128637044</v>
       </c>
       <c r="B5" t="n">
-        <v>56570</v>
+        <v>56597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>128637073</v>
       </c>
       <c r="B6" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601884</v>
       </c>
       <c r="B2" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74604425</v>
       </c>
       <c r="B3" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>75143870</v>
       </c>
       <c r="B4" t="n">
-        <v>106944</v>
+        <v>106950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601884</v>
       </c>
       <c r="B2" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74604425</v>
       </c>
       <c r="B3" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>75143870</v>
       </c>
       <c r="B4" t="n">
-        <v>106950</v>
+        <v>106957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601884</v>
       </c>
       <c r="B2" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74604425</v>
       </c>
       <c r="B3" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>75143870</v>
       </c>
       <c r="B4" t="n">
-        <v>106957</v>
+        <v>106961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128637044</v>
       </c>
       <c r="B5" t="n">
-        <v>56597</v>
+        <v>56600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>128637073</v>
       </c>
       <c r="B6" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601884</v>
       </c>
       <c r="B2" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74604425</v>
       </c>
       <c r="B3" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>75143870</v>
       </c>
       <c r="B4" t="n">
-        <v>106961</v>
+        <v>106969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128637044</v>
       </c>
       <c r="B5" t="n">
-        <v>56600</v>
+        <v>56603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>128637073</v>
       </c>
       <c r="B6" t="n">
-        <v>56605</v>
+        <v>56608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601884</v>
       </c>
       <c r="B2" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74604425</v>
       </c>
       <c r="B3" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>75143870</v>
       </c>
       <c r="B4" t="n">
-        <v>106972</v>
+        <v>106977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601884</v>
       </c>
       <c r="B2" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74604425</v>
       </c>
       <c r="B3" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>75143870</v>
       </c>
       <c r="B4" t="n">
-        <v>106977</v>
+        <v>106985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601884</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74604425</v>
       </c>
       <c r="B3" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>75143870</v>
       </c>
       <c r="B4" t="n">
-        <v>106985</v>
+        <v>106995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128637044</v>
       </c>
       <c r="B5" t="n">
-        <v>56603</v>
+        <v>56605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>128637073</v>
       </c>
       <c r="B6" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74601884</v>
+        <v>128637044</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Moliden. 700m SSV Moliden, Sm</t>
+          <t>Skogsbilväg, Källarp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451317</v>
+        <v>451423</v>
       </c>
       <c r="R2" t="n">
-        <v>6392259</v>
+        <v>6392265</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -740,17 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1976-01-01</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1976-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6E9a 0032. SOM: Lycopodium annotinum. LEG: Ragnar Lernedal</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,35 +773,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Tallhedskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mattis Arveström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Mattis Arveström, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74604425</v>
+        <v>128637009</v>
       </c>
       <c r="B3" t="n">
-        <v>97543</v>
+        <v>56835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,34 +800,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Moliden. 700m SSV Moliden, Sm</t>
+          <t>Skogsbilväg, Källarp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451317</v>
+        <v>451423</v>
       </c>
       <c r="R3" t="n">
-        <v>6392259</v>
+        <v>6392265</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -851,17 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1976-01-01</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1976-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6E9a 0032. SOM: Lycopodium clavatum. LEG: Ragnar Lernedal</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,35 +887,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tallhedskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mattis Arveström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Mattis Arveström, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>75143870</v>
       </c>
       <c r="B4" t="n">
-        <v>106995</v>
+        <v>107516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128637044</v>
+        <v>74601884</v>
       </c>
       <c r="B5" t="n">
-        <v>56605</v>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,51 +1025,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>detektor med heterodyn och tidsexpansion</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogsbilväg, Källarp, Sm</t>
+          <t>Moliden. 700m SSV Moliden, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451423</v>
+        <v>451317</v>
       </c>
       <c r="R5" t="n">
-        <v>6392265</v>
+        <v>6392259</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1090,12 +1079,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>1976-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>1976-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E9a 0032. SOM: Lycopodium annotinum. LEG: Ragnar Lernedal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,26 +1100,35 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Tallhedskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattis Arveström</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattis Arveström, Väg och Miljö AB</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128637073</v>
+        <v>74604425</v>
       </c>
       <c r="B6" t="n">
-        <v>56610</v>
+        <v>97986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,51 +1136,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>detektor med heterodyn och tidsexpansion</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogsbilväg, Källarp, Sm</t>
+          <t>Moliden. 700m SSV Moliden, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451423</v>
+        <v>451317</v>
       </c>
       <c r="R6" t="n">
-        <v>6392265</v>
+        <v>6392259</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1204,12 +1190,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>1976-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>1976-12-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E9a 0032. SOM: Lycopodium clavatum. LEG: Ragnar Lernedal</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,19 +1211,28 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Tallhedskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattis Arveström</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattis Arveström, Väg och Miljö AB</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64890-2021 artfynd.xlsx
+++ b/artfynd/A 64890-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128637044</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128637009</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75143870</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74601884</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,8 +1258,20 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74604425</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>